--- a/Colpatria.xlsx
+++ b/Colpatria.xlsx
@@ -3053,7 +3053,7 @@
       NETWORKDAYS(J2,L2,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N2" s="27"/>
       <c r="O2" s="27"/>
@@ -3200,7 +3200,7 @@
       NETWORKDAYS(J4,L4,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="N4" s="56"/>
       <c r="O4" s="56"/>
@@ -3589,7 +3589,7 @@
       NETWORKDAYS(J9,L9,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N9" s="72"/>
       <c r="O9" s="72"/>
@@ -4270,7 +4270,7 @@
       NETWORKDAYS(J18,L18,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="N18" s="83"/>
       <c r="O18" s="83"/>
@@ -4661,7 +4661,7 @@
       NETWORKDAYS(J23,L23,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="N23" s="83"/>
       <c r="O23" s="83"/>
@@ -5599,7 +5599,7 @@
       NETWORKDAYS(J35,L35,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="N35" s="59"/>
       <c r="O35" s="59"/>
@@ -8381,7 +8381,7 @@
       NETWORKDAYS(J71,L71,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N71" s="150"/>
       <c r="O71" s="150"/>
@@ -8606,7 +8606,7 @@
       NETWORKDAYS(J74,L74,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N74" s="136"/>
       <c r="O74" s="140">
@@ -8681,7 +8681,7 @@
       NETWORKDAYS(J75,L75,Hoja2!$A$2:$A$53)
    )
 )</f>
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N75" s="150"/>
       <c r="O75" s="149">
@@ -9314,7 +9314,7 @@
       </c>
       <c r="E84" s="133"/>
       <c r="F84" s="134" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="G84" s="135">
         <v>100</v>
@@ -9548,41 +9548,41 @@
       <c r="AN87" s="105"/>
     </row>
     <row r="88" spans="1:40" ht="25.5">
-      <c r="A88" s="130" t="s">
+      <c r="A88" s="98" t="s">
         <v>18</v>
       </c>
-      <c r="B88" s="131" t="s">
+      <c r="B88" s="99" t="s">
         <v>352</v>
       </c>
-      <c r="C88" s="132" t="s">
+      <c r="C88" s="93" t="s">
         <v>232</v>
       </c>
-      <c r="D88" s="138" t="s">
+      <c r="D88" s="86" t="s">
         <v>353</v>
       </c>
-      <c r="E88" s="133"/>
-      <c r="F88" s="134" t="s">
+      <c r="E88" s="94"/>
+      <c r="F88" s="95" t="s">
         <v>27</v>
       </c>
-      <c r="G88" s="135">
+      <c r="G88" s="87">
         <v>100</v>
       </c>
-      <c r="H88" s="152"/>
-      <c r="I88" s="140">
+      <c r="H88" s="153"/>
+      <c r="I88" s="59">
         <v>46192</v>
       </c>
-      <c r="J88" s="140">
+      <c r="J88" s="59">
         <v>46192</v>
       </c>
-      <c r="K88" s="140"/>
-      <c r="L88" s="140">
+      <c r="K88" s="59"/>
+      <c r="L88" s="59">
         <v>46192</v>
       </c>
-      <c r="M88" s="152"/>
-      <c r="N88" s="136"/>
-      <c r="O88" s="136"/>
-      <c r="P88" s="136"/>
-      <c r="Q88" s="137" t="s">
+      <c r="M88" s="153"/>
+      <c r="N88" s="77"/>
+      <c r="O88" s="77"/>
+      <c r="P88" s="77"/>
+      <c r="Q88" s="43" t="s">
         <v>354</v>
       </c>
       <c r="R88" s="199" t="s">
